--- a/data/GlobalVariable.xlsx
+++ b/data/GlobalVariable.xlsx
@@ -458,65 +458,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>int32</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>designer</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>constants_name</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="n">
         <v>1</v>
